--- a/reports/TestCases.xlsx
+++ b/reports/TestCases.xlsx
@@ -8154,7 +8154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -8197,34 +8197,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SEC-1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SQL Injection</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>/admin/users</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Review and implement fix</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/TestCases.xlsx
+++ b/reports/TestCases.xlsx
@@ -8154,7 +8154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -8197,6 +8197,102 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SEC-1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Authentication Bypass</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Admin accessible without auth</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>/admin</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Review and implement fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SEC-2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Data Exposure</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>API may expose sensitive data</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>/api/users</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Review and implement fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SEC-3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CORS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Permissive CORS policy</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>/api</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Review and implement fix</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/TestCases.xlsx
+++ b/reports/TestCases.xlsx
@@ -57,7 +57,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -528,7 +530,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -570,7 +577,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -612,7 +624,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -654,7 +671,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -696,7 +718,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -738,7 +765,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -780,7 +812,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -822,7 +859,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -864,7 +906,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -906,7 +953,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -948,7 +1000,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -990,7 +1047,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1094,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1141,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1188,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1235,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1282,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1329,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1376,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1423,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1470,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1517,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1564,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1611,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1658,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1705,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1752,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1799,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1846,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1893,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1940,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1987,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1872,7 +2034,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1914,7 +2081,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1956,7 +2128,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1998,7 +2175,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2222,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2269,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2316,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2363,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2410,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2457,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2504,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2551,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2598,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2645,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2692,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2739,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2786,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2833,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2880,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2927,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2974,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -2754,7 +3021,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -2796,7 +3068,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -2838,7 +3115,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -2880,7 +3162,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -2922,7 +3209,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -2964,7 +3256,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3303,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3350,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3397,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3444,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3491,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3216,7 +3538,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3585,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3632,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3679,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3726,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3773,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3820,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3867,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3914,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3961,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3636,7 +4008,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3678,7 +4055,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3720,7 +4102,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3762,7 +4149,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3804,7 +4196,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3846,7 +4243,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3888,7 +4290,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3930,7 +4337,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -3972,7 +4384,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4431,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4478,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4525,12 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4572,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4619,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4666,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4713,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4760,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4807,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4854,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4901,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4948,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4995,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4560,7 +5042,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4602,7 +5089,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4644,7 +5136,12 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4686,7 +5183,12 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4728,7 +5230,12 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4770,7 +5277,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4812,7 +5324,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4854,7 +5371,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4896,7 +5418,12 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4938,7 +5465,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -4980,7 +5512,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5559,12 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5606,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5653,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5700,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5747,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5794,12 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5841,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5888,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5358,7 +5935,12 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5982,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5442,7 +6029,12 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5484,7 +6076,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5526,7 +6123,12 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5568,7 +6170,12 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5610,7 +6217,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5652,7 +6264,12 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5694,7 +6311,12 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5736,7 +6358,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5778,7 +6405,12 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5820,7 +6452,12 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5862,7 +6499,12 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5904,7 +6546,12 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5946,7 +6593,12 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -5988,7 +6640,12 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6687,12 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6072,7 +6734,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6781,12 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6828,12 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6875,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6922,12 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6969,12 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6324,7 +7016,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6366,7 +7063,12 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6408,7 +7110,12 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6450,7 +7157,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6492,7 +7204,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6534,7 +7251,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6576,7 +7298,12 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6618,7 +7345,12 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6660,7 +7392,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6702,7 +7439,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6744,7 +7486,12 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6786,7 +7533,12 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6828,7 +7580,12 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6870,7 +7627,12 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6912,7 +7674,12 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6954,7 +7721,12 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6996,7 +7768,12 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7815,12 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7080,7 +7862,12 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7909,12 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7956,12 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7206,7 +8003,12 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7248,7 +8050,12 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7290,7 +8097,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7332,7 +8144,12 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7374,7 +8191,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7416,7 +8238,12 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7458,7 +8285,12 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7500,7 +8332,12 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7542,7 +8379,12 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7584,7 +8426,12 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7626,7 +8473,12 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7668,7 +8520,12 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7710,7 +8567,12 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7752,7 +8614,12 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7794,7 +8661,12 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7836,7 +8708,12 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7878,7 +8755,12 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7920,7 +8802,12 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7962,7 +8849,12 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8004,7 +8896,12 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8943,12 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8088,7 +8990,12 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8130,7 +9037,12 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8172,7 +9084,12 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8214,7 +9131,12 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8256,7 +9178,12 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8298,7 +9225,12 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8340,7 +9272,12 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8382,7 +9319,12 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8424,7 +9366,12 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8466,7 +9413,12 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8508,7 +9460,12 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8550,7 +9507,12 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8592,7 +9554,12 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8634,7 +9601,12 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8676,7 +9648,12 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8718,7 +9695,12 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8760,7 +9742,12 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8802,7 +9789,12 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8844,7 +9836,12 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8886,7 +9883,12 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8928,7 +9930,12 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8970,7 +9977,12 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9012,7 +10024,12 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9054,7 +10071,12 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9096,7 +10118,12 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9138,7 +10165,12 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9180,7 +10212,12 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9222,7 +10259,12 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9264,7 +10306,12 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9306,7 +10353,12 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9348,7 +10400,12 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9390,7 +10447,12 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9432,7 +10494,12 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9474,7 +10541,12 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9516,7 +10588,12 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9558,7 +10635,12 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9600,7 +10682,12 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9642,7 +10729,12 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9684,7 +10776,12 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9726,7 +10823,12 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9768,7 +10870,12 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9810,7 +10917,12 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9852,7 +10964,12 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9894,7 +11011,12 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9936,7 +11058,12 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9978,7 +11105,12 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10020,7 +11152,12 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10062,7 +11199,12 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10104,7 +11246,12 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10146,7 +11293,12 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10188,7 +11340,12 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10230,7 +11387,12 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10272,7 +11434,12 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10314,7 +11481,12 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10356,7 +11528,12 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10398,7 +11575,12 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10440,7 +11622,12 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10482,7 +11669,12 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10524,7 +11716,12 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10566,7 +11763,12 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10608,7 +11810,12 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10650,7 +11857,12 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10692,7 +11904,12 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10734,7 +11951,12 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10776,7 +11998,12 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10818,7 +12045,12 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10860,7 +12092,12 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10902,7 +12139,12 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10944,7 +12186,12 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10986,7 +12233,12 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11028,7 +12280,12 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11070,7 +12327,12 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11112,7 +12374,12 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11154,7 +12421,12 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11196,7 +12468,12 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11238,7 +12515,12 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11280,7 +12562,12 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11322,7 +12609,12 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11364,7 +12656,12 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11406,7 +12703,12 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11448,7 +12750,12 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11490,7 +12797,12 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11532,7 +12844,12 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11574,7 +12891,12 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11616,7 +12938,12 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11658,7 +12985,12 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11700,7 +13032,12 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11742,7 +13079,12 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11784,7 +13126,12 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11826,7 +13173,12 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11868,7 +13220,12 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11910,7 +13267,12 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11952,7 +13314,12 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -11994,7 +13361,12 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -12036,7 +13408,12 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -12078,7 +13455,12 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -12120,7 +13502,12 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -12162,7 +13549,12 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -12204,7 +13596,12 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -12246,7 +13643,12 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -12288,7 +13690,12 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -12330,7 +13737,12 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -12372,7 +13784,12 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -12414,7 +13831,12 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -12456,7 +13878,12 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -12498,7 +13925,12 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -12540,7 +13972,12 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -12582,7 +14019,12 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -12624,7 +14066,12 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -12666,7 +14113,12 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -12708,7 +14160,12 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -12750,7 +14207,12 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -12792,7 +14254,12 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -12834,7 +14301,12 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -12876,7 +14348,12 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -12918,7 +14395,12 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -12960,7 +14442,12 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13002,7 +14489,12 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13044,7 +14536,12 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13086,7 +14583,12 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13128,7 +14630,12 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13170,7 +14677,12 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13212,7 +14724,12 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13254,7 +14771,12 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13296,7 +14818,12 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13338,7 +14865,12 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13380,7 +14912,12 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13422,7 +14959,12 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13464,7 +15006,12 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13506,7 +15053,12 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13548,7 +15100,12 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13590,7 +15147,12 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13632,7 +15194,12 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13674,7 +15241,12 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13716,7 +15288,12 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13758,7 +15335,12 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13800,7 +15382,12 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13842,7 +15429,12 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13884,7 +15476,12 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13926,7 +15523,12 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -13968,7 +15570,12 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -14010,7 +15617,12 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -14052,7 +15664,12 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -14094,7 +15711,12 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -14136,7 +15758,12 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -14178,7 +15805,12 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -14220,7 +15852,12 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -14262,7 +15899,12 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -14304,7 +15946,12 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -14346,7 +15993,12 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -14388,7 +16040,12 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -14430,7 +16087,12 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -14472,7 +16134,12 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -14514,7 +16181,12 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -14556,7 +16228,12 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -14598,7 +16275,12 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -14640,7 +16322,12 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -14682,7 +16369,12 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -14724,7 +16416,12 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -14766,7 +16463,12 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
